--- a/DBs/wnba/Results/WNBA_2022_Results.xlsx
+++ b/DBs/wnba/Results/WNBA_2022_Results.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tjsut\TracerSports\WNBA_Elo\Results\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tjsut\tracersports-app\DBs\wnba\Results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F88C4831-7689-4778-A60A-53D42964F41A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F130D582-935C-445F-8BBE-D7EF77DF6CE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{1654EDFA-4626-4D72-A032-E72CC9A130FE}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2354" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2362" uniqueCount="27">
   <si>
     <t>Date</t>
   </si>
@@ -179,8 +179,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{6761A9D6-0284-4780-BB0F-50A0FFF04726}" name="Table1" displayName="Table1" ref="A1:J479" totalsRowShown="0">
-  <autoFilter ref="A1:J479" xr:uid="{6761A9D6-0284-4780-BB0F-50A0FFF04726}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{6761A9D6-0284-4780-BB0F-50A0FFF04726}" name="Table1" displayName="Table1" ref="A1:J481" totalsRowShown="0">
+  <autoFilter ref="A1:J481" xr:uid="{6761A9D6-0284-4780-BB0F-50A0FFF04726}"/>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{9606CA38-2371-480A-B2F8-3A23285B655E}" name="Date" dataDxfId="0"/>
     <tableColumn id="2" xr3:uid="{B29C85CC-3DBC-401B-A183-ABA3F92B96B9}" name="Season"/>
@@ -514,7 +514,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4FB24B2-7646-4F57-8F9C-DF3DFCDB2AF4}">
-  <dimension ref="A1:J479"/>
+  <dimension ref="A1:J481"/>
   <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="9.9140625" bestFit="1" customWidth="1"/>
@@ -11314,31 +11314,31 @@
     </row>
     <row r="338" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A338" s="1">
-        <v>44770</v>
+        <v>44768</v>
       </c>
       <c r="B338">
         <v>2022</v>
       </c>
       <c r="C338" t="s">
-        <v>10</v>
-      </c>
-      <c r="D338" t="s">
-        <v>11</v>
+        <v>23</v>
+      </c>
+      <c r="D338">
+        <v>0.1</v>
       </c>
       <c r="E338" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="F338" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G338" t="s">
         <v>25</v>
       </c>
       <c r="H338">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I338">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="J338">
         <v>0</v>
@@ -11346,31 +11346,31 @@
     </row>
     <row r="339" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A339" s="1">
-        <v>44770</v>
+        <v>44768</v>
       </c>
       <c r="B339">
         <v>2022</v>
       </c>
       <c r="C339" t="s">
-        <v>10</v>
-      </c>
-      <c r="D339" t="s">
-        <v>11</v>
+        <v>23</v>
+      </c>
+      <c r="D339">
+        <v>0.1</v>
       </c>
       <c r="E339" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F339" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="G339" t="s">
         <v>26</v>
       </c>
       <c r="H339">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="I339">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J339">
         <v>0</v>
@@ -11390,19 +11390,19 @@
         <v>11</v>
       </c>
       <c r="E340" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F340" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G340" t="s">
         <v>25</v>
       </c>
       <c r="H340">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="I340">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="J340">
         <v>0</v>
@@ -11422,19 +11422,19 @@
         <v>11</v>
       </c>
       <c r="E341" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F341" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G341" t="s">
         <v>26</v>
       </c>
       <c r="H341">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="I341">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="J341">
         <v>0</v>
@@ -11454,19 +11454,19 @@
         <v>11</v>
       </c>
       <c r="E342" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F342" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G342" t="s">
         <v>25</v>
       </c>
       <c r="H342">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="I342">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="J342">
         <v>0</v>
@@ -11486,19 +11486,19 @@
         <v>11</v>
       </c>
       <c r="E343" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F343" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="G343" t="s">
         <v>26</v>
       </c>
       <c r="H343">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="I343">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="J343">
         <v>0</v>
@@ -11518,19 +11518,19 @@
         <v>11</v>
       </c>
       <c r="E344" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F344" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="G344" t="s">
         <v>25</v>
       </c>
       <c r="H344">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="I344">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="J344">
         <v>0</v>
@@ -11550,19 +11550,19 @@
         <v>11</v>
       </c>
       <c r="E345" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F345" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G345" t="s">
         <v>26</v>
       </c>
       <c r="H345">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="I345">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="J345">
         <v>0</v>
@@ -11570,7 +11570,7 @@
     </row>
     <row r="346" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A346" s="1">
-        <v>44771</v>
+        <v>44770</v>
       </c>
       <c r="B346">
         <v>2022</v>
@@ -11582,19 +11582,19 @@
         <v>11</v>
       </c>
       <c r="E346" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F346" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="G346" t="s">
         <v>25</v>
       </c>
       <c r="H346">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="I346">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J346">
         <v>0</v>
@@ -11602,7 +11602,7 @@
     </row>
     <row r="347" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A347" s="1">
-        <v>44771</v>
+        <v>44770</v>
       </c>
       <c r="B347">
         <v>2022</v>
@@ -11614,19 +11614,19 @@
         <v>11</v>
       </c>
       <c r="E347" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F347" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G347" t="s">
         <v>26</v>
       </c>
       <c r="H347">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I347">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="J347">
         <v>0</v>
@@ -11646,19 +11646,19 @@
         <v>11</v>
       </c>
       <c r="E348" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="F348" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G348" t="s">
         <v>25</v>
       </c>
       <c r="H348">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="I348">
-        <v>72</v>
+        <v>89</v>
       </c>
       <c r="J348">
         <v>0</v>
@@ -11678,19 +11678,19 @@
         <v>11</v>
       </c>
       <c r="E349" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F349" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="G349" t="s">
         <v>26</v>
       </c>
       <c r="H349">
-        <v>72</v>
+        <v>89</v>
       </c>
       <c r="I349">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="J349">
         <v>0</v>
@@ -11698,7 +11698,7 @@
     </row>
     <row r="350" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A350" s="1">
-        <v>44772</v>
+        <v>44771</v>
       </c>
       <c r="B350">
         <v>2022</v>
@@ -11710,19 +11710,19 @@
         <v>11</v>
       </c>
       <c r="E350" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F350" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="G350" t="s">
         <v>25</v>
       </c>
       <c r="H350">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="I350">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="J350">
         <v>0</v>
@@ -11730,7 +11730,7 @@
     </row>
     <row r="351" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A351" s="1">
-        <v>44772</v>
+        <v>44771</v>
       </c>
       <c r="B351">
         <v>2022</v>
@@ -11742,19 +11742,19 @@
         <v>11</v>
       </c>
       <c r="E351" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F351" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G351" t="s">
         <v>26</v>
       </c>
       <c r="H351">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="I351">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="J351">
         <v>0</v>
@@ -11774,19 +11774,19 @@
         <v>11</v>
       </c>
       <c r="E352" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="F352" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="G352" t="s">
         <v>25</v>
       </c>
       <c r="H352">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I352">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="J352">
         <v>0</v>
@@ -11806,19 +11806,19 @@
         <v>11</v>
       </c>
       <c r="E353" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="F353" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="G353" t="s">
         <v>26</v>
       </c>
       <c r="H353">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="I353">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J353">
         <v>0</v>
@@ -11826,7 +11826,7 @@
     </row>
     <row r="354" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A354" s="1">
-        <v>44773</v>
+        <v>44772</v>
       </c>
       <c r="B354">
         <v>2022</v>
@@ -11838,27 +11838,27 @@
         <v>11</v>
       </c>
       <c r="E354" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F354" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="G354" t="s">
         <v>25</v>
       </c>
       <c r="H354">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="I354">
-        <v>92</v>
+        <v>77</v>
       </c>
       <c r="J354">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="355" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A355" s="1">
-        <v>44773</v>
+        <v>44772</v>
       </c>
       <c r="B355">
         <v>2022</v>
@@ -11870,22 +11870,22 @@
         <v>11</v>
       </c>
       <c r="E355" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="F355" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G355" t="s">
         <v>26</v>
       </c>
       <c r="H355">
-        <v>92</v>
+        <v>77</v>
       </c>
       <c r="I355">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="J355">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="356" spans="1:10" x14ac:dyDescent="0.35">
@@ -11902,22 +11902,22 @@
         <v>11</v>
       </c>
       <c r="E356" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F356" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G356" t="s">
         <v>25</v>
       </c>
       <c r="H356">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I356">
-        <v>69</v>
+        <v>92</v>
       </c>
       <c r="J356">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="357" spans="1:10" x14ac:dyDescent="0.35">
@@ -11934,22 +11934,22 @@
         <v>11</v>
       </c>
       <c r="E357" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F357" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="G357" t="s">
         <v>26</v>
       </c>
       <c r="H357">
-        <v>69</v>
+        <v>92</v>
       </c>
       <c r="I357">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="J357">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="358" spans="1:10" x14ac:dyDescent="0.35">
@@ -11966,19 +11966,19 @@
         <v>11</v>
       </c>
       <c r="E358" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="F358" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G358" t="s">
         <v>25</v>
       </c>
       <c r="H358">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="I358">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="J358">
         <v>0</v>
@@ -11998,19 +11998,19 @@
         <v>11</v>
       </c>
       <c r="E359" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F359" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="G359" t="s">
         <v>26</v>
       </c>
       <c r="H359">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="I359">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="J359">
         <v>0</v>
@@ -12030,19 +12030,19 @@
         <v>11</v>
       </c>
       <c r="E360" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F360" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G360" t="s">
         <v>25</v>
       </c>
       <c r="H360">
-        <v>69</v>
+        <v>84</v>
       </c>
       <c r="I360">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="J360">
         <v>0</v>
@@ -12062,19 +12062,19 @@
         <v>11</v>
       </c>
       <c r="E361" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F361" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G361" t="s">
         <v>26</v>
       </c>
       <c r="H361">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="I361">
-        <v>69</v>
+        <v>84</v>
       </c>
       <c r="J361">
         <v>0</v>
@@ -12094,19 +12094,19 @@
         <v>11</v>
       </c>
       <c r="E362" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F362" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G362" t="s">
         <v>25</v>
       </c>
       <c r="H362">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="I362">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="J362">
         <v>0</v>
@@ -12126,19 +12126,19 @@
         <v>11</v>
       </c>
       <c r="E363" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F363" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G363" t="s">
         <v>26</v>
       </c>
       <c r="H363">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="I363">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="J363">
         <v>0</v>
@@ -12146,7 +12146,7 @@
     </row>
     <row r="364" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A364" s="1">
-        <v>44775</v>
+        <v>44773</v>
       </c>
       <c r="B364">
         <v>2022</v>
@@ -12158,16 +12158,16 @@
         <v>11</v>
       </c>
       <c r="E364" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F364" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="G364" t="s">
         <v>25</v>
       </c>
       <c r="H364">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="I364">
         <v>78</v>
@@ -12178,7 +12178,7 @@
     </row>
     <row r="365" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A365" s="1">
-        <v>44775</v>
+        <v>44773</v>
       </c>
       <c r="B365">
         <v>2022</v>
@@ -12190,10 +12190,10 @@
         <v>11</v>
       </c>
       <c r="E365" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="F365" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="G365" t="s">
         <v>26</v>
@@ -12202,7 +12202,7 @@
         <v>78</v>
       </c>
       <c r="I365">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="J365">
         <v>0</v>
@@ -12222,19 +12222,19 @@
         <v>11</v>
       </c>
       <c r="E366" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F366" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G366" t="s">
         <v>25</v>
       </c>
       <c r="H366">
-        <v>63</v>
+        <v>84</v>
       </c>
       <c r="I366">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="J366">
         <v>0</v>
@@ -12254,19 +12254,19 @@
         <v>11</v>
       </c>
       <c r="E367" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F367" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="G367" t="s">
         <v>26</v>
       </c>
       <c r="H367">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="I367">
-        <v>63</v>
+        <v>84</v>
       </c>
       <c r="J367">
         <v>0</v>
@@ -12286,19 +12286,19 @@
         <v>11</v>
       </c>
       <c r="E368" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F368" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="G368" t="s">
         <v>25</v>
       </c>
       <c r="H368">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="I368">
-        <v>102</v>
+        <v>87</v>
       </c>
       <c r="J368">
         <v>0</v>
@@ -12318,19 +12318,19 @@
         <v>11</v>
       </c>
       <c r="E369" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="F369" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G369" t="s">
         <v>26</v>
       </c>
       <c r="H369">
-        <v>102</v>
+        <v>87</v>
       </c>
       <c r="I369">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="J369">
         <v>0</v>
@@ -12350,10 +12350,10 @@
         <v>11</v>
       </c>
       <c r="E370" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="F370" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G370" t="s">
         <v>25</v>
@@ -12362,7 +12362,7 @@
         <v>73</v>
       </c>
       <c r="I370">
-        <v>83</v>
+        <v>102</v>
       </c>
       <c r="J370">
         <v>0</v>
@@ -12382,16 +12382,16 @@
         <v>11</v>
       </c>
       <c r="E371" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F371" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="G371" t="s">
         <v>26</v>
       </c>
       <c r="H371">
-        <v>83</v>
+        <v>102</v>
       </c>
       <c r="I371">
         <v>73</v>
@@ -12402,7 +12402,7 @@
     </row>
     <row r="372" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A372" s="1">
-        <v>44776</v>
+        <v>44775</v>
       </c>
       <c r="B372">
         <v>2022</v>
@@ -12414,19 +12414,19 @@
         <v>11</v>
       </c>
       <c r="E372" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F372" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="G372" t="s">
         <v>25</v>
       </c>
       <c r="H372">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="I372">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="J372">
         <v>0</v>
@@ -12434,7 +12434,7 @@
     </row>
     <row r="373" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A373" s="1">
-        <v>44776</v>
+        <v>44775</v>
       </c>
       <c r="B373">
         <v>2022</v>
@@ -12446,19 +12446,19 @@
         <v>11</v>
       </c>
       <c r="E373" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F373" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="G373" t="s">
         <v>26</v>
       </c>
       <c r="H373">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="I373">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="J373">
         <v>0</v>
@@ -12478,19 +12478,19 @@
         <v>11</v>
       </c>
       <c r="E374" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F374" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="G374" t="s">
         <v>25</v>
       </c>
       <c r="H374">
-        <v>61</v>
+        <v>81</v>
       </c>
       <c r="I374">
-        <v>64</v>
+        <v>91</v>
       </c>
       <c r="J374">
         <v>0</v>
@@ -12510,19 +12510,19 @@
         <v>11</v>
       </c>
       <c r="E375" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="F375" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G375" t="s">
         <v>26</v>
       </c>
       <c r="H375">
-        <v>64</v>
+        <v>91</v>
       </c>
       <c r="I375">
-        <v>61</v>
+        <v>81</v>
       </c>
       <c r="J375">
         <v>0</v>
@@ -12542,19 +12542,19 @@
         <v>11</v>
       </c>
       <c r="E376" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F376" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="G376" t="s">
         <v>25</v>
       </c>
       <c r="H376">
-        <v>77</v>
+        <v>61</v>
       </c>
       <c r="I376">
-        <v>89</v>
+        <v>64</v>
       </c>
       <c r="J376">
         <v>0</v>
@@ -12574,19 +12574,19 @@
         <v>11</v>
       </c>
       <c r="E377" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F377" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G377" t="s">
         <v>26</v>
       </c>
       <c r="H377">
-        <v>89</v>
+        <v>64</v>
       </c>
       <c r="I377">
-        <v>77</v>
+        <v>61</v>
       </c>
       <c r="J377">
         <v>0</v>
@@ -12594,7 +12594,7 @@
     </row>
     <row r="378" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A378" s="1">
-        <v>44777</v>
+        <v>44776</v>
       </c>
       <c r="B378">
         <v>2022</v>
@@ -12606,19 +12606,19 @@
         <v>11</v>
       </c>
       <c r="E378" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F378" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G378" t="s">
         <v>25</v>
       </c>
       <c r="H378">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="I378">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="J378">
         <v>0</v>
@@ -12626,7 +12626,7 @@
     </row>
     <row r="379" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A379" s="1">
-        <v>44777</v>
+        <v>44776</v>
       </c>
       <c r="B379">
         <v>2022</v>
@@ -12638,19 +12638,19 @@
         <v>11</v>
       </c>
       <c r="E379" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F379" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G379" t="s">
         <v>26</v>
       </c>
       <c r="H379">
+        <v>89</v>
+      </c>
+      <c r="I379">
         <v>77</v>
-      </c>
-      <c r="I379">
-        <v>64</v>
       </c>
       <c r="J379">
         <v>0</v>
@@ -12670,19 +12670,19 @@
         <v>11</v>
       </c>
       <c r="E380" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="F380" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G380" t="s">
         <v>25</v>
       </c>
       <c r="H380">
-        <v>80</v>
+        <v>64</v>
       </c>
       <c r="I380">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="J380">
         <v>0</v>
@@ -12702,19 +12702,19 @@
         <v>11</v>
       </c>
       <c r="E381" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F381" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="G381" t="s">
         <v>26</v>
       </c>
       <c r="H381">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="I381">
-        <v>80</v>
+        <v>64</v>
       </c>
       <c r="J381">
         <v>0</v>
@@ -12722,7 +12722,7 @@
     </row>
     <row r="382" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A382" s="1">
-        <v>44778</v>
+        <v>44777</v>
       </c>
       <c r="B382">
         <v>2022</v>
@@ -12734,19 +12734,19 @@
         <v>11</v>
       </c>
       <c r="E382" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="F382" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G382" t="s">
         <v>25</v>
       </c>
       <c r="H382">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="I382">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="J382">
         <v>0</v>
@@ -12754,7 +12754,7 @@
     </row>
     <row r="383" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A383" s="1">
-        <v>44778</v>
+        <v>44777</v>
       </c>
       <c r="B383">
         <v>2022</v>
@@ -12766,19 +12766,19 @@
         <v>11</v>
       </c>
       <c r="E383" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F383" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="G383" t="s">
         <v>26</v>
       </c>
       <c r="H383">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="I383">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="J383">
         <v>0</v>
@@ -12798,19 +12798,19 @@
         <v>11</v>
       </c>
       <c r="E384" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F384" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G384" t="s">
         <v>25</v>
       </c>
       <c r="H384">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="I384">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="J384">
         <v>0</v>
@@ -12830,19 +12830,19 @@
         <v>11</v>
       </c>
       <c r="E385" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F385" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G385" t="s">
         <v>26</v>
       </c>
       <c r="H385">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="I385">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="J385">
         <v>0</v>
@@ -12850,7 +12850,7 @@
     </row>
     <row r="386" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A386" s="1">
-        <v>44779</v>
+        <v>44778</v>
       </c>
       <c r="B386">
         <v>2022</v>
@@ -12862,27 +12862,27 @@
         <v>11</v>
       </c>
       <c r="E386" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F386" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="G386" t="s">
         <v>25</v>
       </c>
       <c r="H386">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="I386">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="J386">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="387" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A387" s="1">
-        <v>44779</v>
+        <v>44778</v>
       </c>
       <c r="B387">
         <v>2022</v>
@@ -12894,22 +12894,22 @@
         <v>11</v>
       </c>
       <c r="E387" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F387" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="G387" t="s">
         <v>26</v>
       </c>
       <c r="H387">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="I387">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="J387">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="388" spans="1:10" x14ac:dyDescent="0.35">
@@ -12926,22 +12926,22 @@
         <v>11</v>
       </c>
       <c r="E388" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="F388" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="G388" t="s">
         <v>25</v>
       </c>
       <c r="H388">
-        <v>62</v>
+        <v>91</v>
       </c>
       <c r="I388">
-        <v>76</v>
+        <v>95</v>
       </c>
       <c r="J388">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="389" spans="1:10" x14ac:dyDescent="0.35">
@@ -12958,27 +12958,27 @@
         <v>11</v>
       </c>
       <c r="E389" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F389" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="G389" t="s">
         <v>26</v>
       </c>
       <c r="H389">
-        <v>76</v>
+        <v>95</v>
       </c>
       <c r="I389">
-        <v>62</v>
+        <v>91</v>
       </c>
       <c r="J389">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="390" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A390" s="1">
-        <v>44780</v>
+        <v>44779</v>
       </c>
       <c r="B390">
         <v>2022</v>
@@ -12990,19 +12990,19 @@
         <v>11</v>
       </c>
       <c r="E390" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="F390" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="G390" t="s">
         <v>25</v>
       </c>
       <c r="H390">
-        <v>91</v>
+        <v>62</v>
       </c>
       <c r="I390">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="J390">
         <v>0</v>
@@ -13010,7 +13010,7 @@
     </row>
     <row r="391" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A391" s="1">
-        <v>44780</v>
+        <v>44779</v>
       </c>
       <c r="B391">
         <v>2022</v>
@@ -13022,19 +13022,19 @@
         <v>11</v>
       </c>
       <c r="E391" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F391" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="G391" t="s">
         <v>26</v>
       </c>
       <c r="H391">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="I391">
-        <v>91</v>
+        <v>62</v>
       </c>
       <c r="J391">
         <v>0</v>
@@ -13054,19 +13054,19 @@
         <v>11</v>
       </c>
       <c r="E392" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F392" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G392" t="s">
         <v>25</v>
       </c>
       <c r="H392">
-        <v>71</v>
+        <v>91</v>
       </c>
       <c r="I392">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="J392">
         <v>0</v>
@@ -13086,19 +13086,19 @@
         <v>11</v>
       </c>
       <c r="E393" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F393" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G393" t="s">
         <v>26</v>
       </c>
       <c r="H393">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="I393">
-        <v>71</v>
+        <v>91</v>
       </c>
       <c r="J393">
         <v>0</v>
@@ -13118,16 +13118,16 @@
         <v>11</v>
       </c>
       <c r="E394" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F394" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G394" t="s">
         <v>25</v>
       </c>
       <c r="H394">
-        <v>89</v>
+        <v>71</v>
       </c>
       <c r="I394">
         <v>81</v>
@@ -13150,10 +13150,10 @@
         <v>11</v>
       </c>
       <c r="E395" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F395" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="G395" t="s">
         <v>26</v>
@@ -13162,7 +13162,7 @@
         <v>81</v>
       </c>
       <c r="I395">
-        <v>89</v>
+        <v>71</v>
       </c>
       <c r="J395">
         <v>0</v>
@@ -13182,19 +13182,19 @@
         <v>11</v>
       </c>
       <c r="E396" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="F396" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="G396" t="s">
         <v>25</v>
       </c>
       <c r="H396">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="I396">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="J396">
         <v>0</v>
@@ -13214,19 +13214,19 @@
         <v>11</v>
       </c>
       <c r="E397" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F397" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="G397" t="s">
         <v>26</v>
       </c>
       <c r="H397">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="I397">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="J397">
         <v>0</v>
@@ -13234,7 +13234,7 @@
     </row>
     <row r="398" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A398" s="1">
-        <v>44781</v>
+        <v>44780</v>
       </c>
       <c r="B398">
         <v>2022</v>
@@ -13246,19 +13246,19 @@
         <v>11</v>
       </c>
       <c r="E398" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F398" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="G398" t="s">
         <v>25</v>
       </c>
       <c r="H398">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="I398">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="J398">
         <v>0</v>
@@ -13266,7 +13266,7 @@
     </row>
     <row r="399" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A399" s="1">
-        <v>44781</v>
+        <v>44780</v>
       </c>
       <c r="B399">
         <v>2022</v>
@@ -13278,19 +13278,19 @@
         <v>11</v>
       </c>
       <c r="E399" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="F399" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G399" t="s">
         <v>26</v>
       </c>
       <c r="H399">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="I399">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="J399">
         <v>0</v>
@@ -13298,7 +13298,7 @@
     </row>
     <row r="400" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A400" s="1">
-        <v>44782</v>
+        <v>44781</v>
       </c>
       <c r="B400">
         <v>2022</v>
@@ -13310,19 +13310,19 @@
         <v>11</v>
       </c>
       <c r="E400" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F400" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G400" t="s">
         <v>25</v>
       </c>
       <c r="H400">
-        <v>111</v>
+        <v>77</v>
       </c>
       <c r="I400">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="J400">
         <v>0</v>
@@ -13330,7 +13330,7 @@
     </row>
     <row r="401" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A401" s="1">
-        <v>44782</v>
+        <v>44781</v>
       </c>
       <c r="B401">
         <v>2022</v>
@@ -13342,19 +13342,19 @@
         <v>11</v>
       </c>
       <c r="E401" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F401" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="G401" t="s">
         <v>26</v>
       </c>
       <c r="H401">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="I401">
-        <v>111</v>
+        <v>77</v>
       </c>
       <c r="J401">
         <v>0</v>
@@ -13374,19 +13374,19 @@
         <v>11</v>
       </c>
       <c r="E402" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F402" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G402" t="s">
         <v>25</v>
       </c>
       <c r="H402">
-        <v>97</v>
+        <v>111</v>
       </c>
       <c r="I402">
-        <v>71</v>
+        <v>100</v>
       </c>
       <c r="J402">
         <v>0</v>
@@ -13406,19 +13406,19 @@
         <v>11</v>
       </c>
       <c r="E403" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F403" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G403" t="s">
         <v>26</v>
       </c>
       <c r="H403">
-        <v>71</v>
+        <v>100</v>
       </c>
       <c r="I403">
-        <v>97</v>
+        <v>111</v>
       </c>
       <c r="J403">
         <v>0</v>
@@ -13438,19 +13438,19 @@
         <v>11</v>
       </c>
       <c r="E404" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F404" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="G404" t="s">
         <v>25</v>
       </c>
       <c r="H404">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="I404">
-        <v>97</v>
+        <v>71</v>
       </c>
       <c r="J404">
         <v>0</v>
@@ -13470,19 +13470,19 @@
         <v>11</v>
       </c>
       <c r="E405" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="F405" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G405" t="s">
         <v>26</v>
       </c>
       <c r="H405">
+        <v>71</v>
+      </c>
+      <c r="I405">
         <v>97</v>
-      </c>
-      <c r="I405">
-        <v>90</v>
       </c>
       <c r="J405">
         <v>0</v>
@@ -13490,7 +13490,7 @@
     </row>
     <row r="406" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A406" s="1">
-        <v>44783</v>
+        <v>44782</v>
       </c>
       <c r="B406">
         <v>2022</v>
@@ -13502,19 +13502,19 @@
         <v>11</v>
       </c>
       <c r="E406" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="F406" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G406" t="s">
         <v>25</v>
       </c>
       <c r="H406">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I406">
-        <v>73</v>
+        <v>97</v>
       </c>
       <c r="J406">
         <v>0</v>
@@ -13522,7 +13522,7 @@
     </row>
     <row r="407" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A407" s="1">
-        <v>44783</v>
+        <v>44782</v>
       </c>
       <c r="B407">
         <v>2022</v>
@@ -13534,19 +13534,19 @@
         <v>11</v>
       </c>
       <c r="E407" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F407" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="G407" t="s">
         <v>26</v>
       </c>
       <c r="H407">
-        <v>73</v>
+        <v>97</v>
       </c>
       <c r="I407">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="J407">
         <v>0</v>
@@ -13566,19 +13566,19 @@
         <v>11</v>
       </c>
       <c r="E408" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F408" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="G408" t="s">
         <v>25</v>
       </c>
       <c r="H408">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="I408">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="J408">
         <v>0</v>
@@ -13598,19 +13598,19 @@
         <v>11</v>
       </c>
       <c r="E409" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F409" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="G409" t="s">
         <v>26</v>
       </c>
       <c r="H409">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="I409">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="J409">
         <v>0</v>
@@ -13618,7 +13618,7 @@
     </row>
     <row r="410" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A410" s="1">
-        <v>44784</v>
+        <v>44783</v>
       </c>
       <c r="B410">
         <v>2022</v>
@@ -13630,19 +13630,19 @@
         <v>11</v>
       </c>
       <c r="E410" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F410" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G410" t="s">
         <v>25</v>
       </c>
       <c r="H410">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="I410">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="J410">
         <v>0</v>
@@ -13650,7 +13650,7 @@
     </row>
     <row r="411" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A411" s="1">
-        <v>44784</v>
+        <v>44783</v>
       </c>
       <c r="B411">
         <v>2022</v>
@@ -13662,19 +13662,19 @@
         <v>11</v>
       </c>
       <c r="E411" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F411" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G411" t="s">
         <v>26</v>
       </c>
       <c r="H411">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="I411">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="J411">
         <v>0</v>
@@ -13694,19 +13694,19 @@
         <v>11</v>
       </c>
       <c r="E412" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F412" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="G412" t="s">
         <v>25</v>
       </c>
       <c r="H412">
-        <v>78</v>
+        <v>93</v>
       </c>
       <c r="I412">
-        <v>89</v>
+        <v>69</v>
       </c>
       <c r="J412">
         <v>0</v>
@@ -13726,19 +13726,19 @@
         <v>11</v>
       </c>
       <c r="E413" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="F413" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G413" t="s">
         <v>26</v>
       </c>
       <c r="H413">
-        <v>89</v>
+        <v>69</v>
       </c>
       <c r="I413">
-        <v>78</v>
+        <v>93</v>
       </c>
       <c r="J413">
         <v>0</v>
@@ -13746,7 +13746,7 @@
     </row>
     <row r="414" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A414" s="1">
-        <v>44785</v>
+        <v>44784</v>
       </c>
       <c r="B414">
         <v>2022</v>
@@ -13758,19 +13758,19 @@
         <v>11</v>
       </c>
       <c r="E414" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="F414" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G414" t="s">
         <v>25</v>
       </c>
       <c r="H414">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="I414">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="J414">
         <v>0</v>
@@ -13778,7 +13778,7 @@
     </row>
     <row r="415" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A415" s="1">
-        <v>44785</v>
+        <v>44784</v>
       </c>
       <c r="B415">
         <v>2022</v>
@@ -13790,19 +13790,19 @@
         <v>11</v>
       </c>
       <c r="E415" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F415" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="G415" t="s">
         <v>26</v>
       </c>
       <c r="H415">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="I415">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="J415">
         <v>0</v>
@@ -13822,16 +13822,16 @@
         <v>11</v>
       </c>
       <c r="E416" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F416" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="G416" t="s">
         <v>25</v>
       </c>
       <c r="H416">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="I416">
         <v>70</v>
@@ -13854,10 +13854,10 @@
         <v>11</v>
       </c>
       <c r="E417" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F417" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G417" t="s">
         <v>26</v>
@@ -13866,7 +13866,7 @@
         <v>70</v>
       </c>
       <c r="I417">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J417">
         <v>0</v>
@@ -13886,19 +13886,19 @@
         <v>11</v>
       </c>
       <c r="E418" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F418" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G418" t="s">
         <v>25</v>
       </c>
       <c r="H418">
-        <v>96</v>
+        <v>82</v>
       </c>
       <c r="I418">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="J418">
         <v>0</v>
@@ -13918,19 +13918,19 @@
         <v>11</v>
       </c>
       <c r="E419" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F419" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="G419" t="s">
         <v>26</v>
       </c>
       <c r="H419">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I419">
-        <v>96</v>
+        <v>82</v>
       </c>
       <c r="J419">
         <v>0</v>
@@ -13950,19 +13950,19 @@
         <v>11</v>
       </c>
       <c r="E420" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F420" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G420" t="s">
         <v>25</v>
       </c>
       <c r="H420">
-        <v>74</v>
+        <v>96</v>
       </c>
       <c r="I420">
-        <v>86</v>
+        <v>69</v>
       </c>
       <c r="J420">
         <v>0</v>
@@ -13982,19 +13982,19 @@
         <v>11</v>
       </c>
       <c r="E421" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F421" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="G421" t="s">
         <v>26</v>
       </c>
       <c r="H421">
-        <v>86</v>
+        <v>69</v>
       </c>
       <c r="I421">
-        <v>74</v>
+        <v>96</v>
       </c>
       <c r="J421">
         <v>0</v>
@@ -14002,7 +14002,7 @@
     </row>
     <row r="422" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A422" s="1">
-        <v>44787</v>
+        <v>44785</v>
       </c>
       <c r="B422">
         <v>2022</v>
@@ -14014,19 +14014,19 @@
         <v>11</v>
       </c>
       <c r="E422" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="F422" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="G422" t="s">
         <v>25</v>
       </c>
       <c r="H422">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="I422">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="J422">
         <v>0</v>
@@ -14034,7 +14034,7 @@
     </row>
     <row r="423" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A423" s="1">
-        <v>44787</v>
+        <v>44785</v>
       </c>
       <c r="B423">
         <v>2022</v>
@@ -14046,19 +14046,19 @@
         <v>11</v>
       </c>
       <c r="E423" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="F423" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="G423" t="s">
         <v>26</v>
       </c>
       <c r="H423">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="I423">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="J423">
         <v>0</v>
@@ -14078,19 +14078,19 @@
         <v>11</v>
       </c>
       <c r="E424" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="F424" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="G424" t="s">
         <v>25</v>
       </c>
       <c r="H424">
-        <v>116</v>
+        <v>83</v>
       </c>
       <c r="I424">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="J424">
         <v>0</v>
@@ -14110,19 +14110,19 @@
         <v>11</v>
       </c>
       <c r="E425" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F425" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="G425" t="s">
         <v>26</v>
       </c>
       <c r="H425">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="I425">
-        <v>116</v>
+        <v>83</v>
       </c>
       <c r="J425">
         <v>0</v>
@@ -14142,19 +14142,19 @@
         <v>11</v>
       </c>
       <c r="E426" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="F426" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="G426" t="s">
         <v>25</v>
       </c>
       <c r="H426">
-        <v>100</v>
+        <v>116</v>
       </c>
       <c r="I426">
-        <v>109</v>
+        <v>88</v>
       </c>
       <c r="J426">
         <v>0</v>
@@ -14174,19 +14174,19 @@
         <v>11</v>
       </c>
       <c r="E427" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="F427" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="G427" t="s">
         <v>26</v>
       </c>
       <c r="H427">
-        <v>109</v>
+        <v>88</v>
       </c>
       <c r="I427">
-        <v>100</v>
+        <v>116</v>
       </c>
       <c r="J427">
         <v>0</v>
@@ -14206,19 +14206,19 @@
         <v>11</v>
       </c>
       <c r="E428" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F428" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="G428" t="s">
         <v>25</v>
       </c>
       <c r="H428">
-        <v>83</v>
+        <v>100</v>
       </c>
       <c r="I428">
-        <v>87</v>
+        <v>109</v>
       </c>
       <c r="J428">
         <v>0</v>
@@ -14238,19 +14238,19 @@
         <v>11</v>
       </c>
       <c r="E429" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="F429" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="G429" t="s">
         <v>26</v>
       </c>
       <c r="H429">
-        <v>87</v>
+        <v>109</v>
       </c>
       <c r="I429">
-        <v>83</v>
+        <v>100</v>
       </c>
       <c r="J429">
         <v>0</v>
@@ -14270,19 +14270,19 @@
         <v>11</v>
       </c>
       <c r="E430" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F430" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G430" t="s">
         <v>25</v>
       </c>
       <c r="H430">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I430">
-        <v>67</v>
+        <v>87</v>
       </c>
       <c r="J430">
         <v>0</v>
@@ -14302,19 +14302,19 @@
         <v>11</v>
       </c>
       <c r="E431" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F431" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G431" t="s">
         <v>26</v>
       </c>
       <c r="H431">
-        <v>67</v>
+        <v>87</v>
       </c>
       <c r="I431">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J431">
         <v>0</v>
@@ -14334,19 +14334,19 @@
         <v>11</v>
       </c>
       <c r="E432" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F432" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G432" t="s">
         <v>25</v>
       </c>
       <c r="H432">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I432">
-        <v>95</v>
+        <v>67</v>
       </c>
       <c r="J432">
         <v>0</v>
@@ -14366,19 +14366,19 @@
         <v>11</v>
       </c>
       <c r="E433" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F433" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G433" t="s">
         <v>26</v>
       </c>
       <c r="H433">
-        <v>95</v>
+        <v>67</v>
       </c>
       <c r="I433">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J433">
         <v>0</v>
@@ -14386,31 +14386,31 @@
     </row>
     <row r="434" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A434" s="1">
-        <v>44790</v>
+        <v>44787</v>
       </c>
       <c r="B434">
         <v>2022</v>
       </c>
       <c r="C434" t="s">
-        <v>23</v>
-      </c>
-      <c r="D434">
-        <v>1</v>
+        <v>10</v>
+      </c>
+      <c r="D434" t="s">
+        <v>11</v>
       </c>
       <c r="E434" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="F434" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="G434" t="s">
         <v>25</v>
       </c>
       <c r="H434">
-        <v>98</v>
+        <v>83</v>
       </c>
       <c r="I434">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="J434">
         <v>0</v>
@@ -14418,31 +14418,31 @@
     </row>
     <row r="435" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A435" s="1">
-        <v>44790</v>
+        <v>44787</v>
       </c>
       <c r="B435">
         <v>2022</v>
       </c>
       <c r="C435" t="s">
-        <v>23</v>
-      </c>
-      <c r="D435">
-        <v>1</v>
+        <v>10</v>
+      </c>
+      <c r="D435" t="s">
+        <v>11</v>
       </c>
       <c r="E435" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="F435" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="G435" t="s">
         <v>26</v>
       </c>
       <c r="H435">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="I435">
-        <v>98</v>
+        <v>83</v>
       </c>
       <c r="J435">
         <v>0</v>
@@ -14462,19 +14462,19 @@
         <v>1</v>
       </c>
       <c r="E436" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F436" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="G436" t="s">
         <v>25</v>
       </c>
       <c r="H436">
-        <v>63</v>
+        <v>98</v>
       </c>
       <c r="I436">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="J436">
         <v>0</v>
@@ -14494,19 +14494,19 @@
         <v>1</v>
       </c>
       <c r="E437" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F437" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G437" t="s">
         <v>26</v>
       </c>
       <c r="H437">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="I437">
-        <v>63</v>
+        <v>98</v>
       </c>
       <c r="J437">
         <v>0</v>
@@ -14514,7 +14514,7 @@
     </row>
     <row r="438" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A438" s="1">
-        <v>44791</v>
+        <v>44790</v>
       </c>
       <c r="B438">
         <v>2022</v>
@@ -14526,19 +14526,19 @@
         <v>1</v>
       </c>
       <c r="E438" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="F438" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="G438" t="s">
         <v>25</v>
       </c>
       <c r="H438">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="I438">
-        <v>93</v>
+        <v>79</v>
       </c>
       <c r="J438">
         <v>0</v>
@@ -14546,7 +14546,7 @@
     </row>
     <row r="439" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A439" s="1">
-        <v>44791</v>
+        <v>44790</v>
       </c>
       <c r="B439">
         <v>2022</v>
@@ -14558,19 +14558,19 @@
         <v>1</v>
       </c>
       <c r="E439" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F439" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="G439" t="s">
         <v>26</v>
       </c>
       <c r="H439">
-        <v>93</v>
+        <v>79</v>
       </c>
       <c r="I439">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="J439">
         <v>0</v>
@@ -14590,19 +14590,19 @@
         <v>1</v>
       </c>
       <c r="E440" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="F440" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G440" t="s">
         <v>25</v>
       </c>
       <c r="H440">
-        <v>83</v>
+        <v>68</v>
       </c>
       <c r="I440">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="J440">
         <v>0</v>
@@ -14622,19 +14622,19 @@
         <v>1</v>
       </c>
       <c r="E441" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F441" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="G441" t="s">
         <v>26</v>
       </c>
       <c r="H441">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="I441">
-        <v>83</v>
+        <v>68</v>
       </c>
       <c r="J441">
         <v>0</v>
@@ -14642,7 +14642,7 @@
     </row>
     <row r="442" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A442" s="1">
-        <v>44793</v>
+        <v>44791</v>
       </c>
       <c r="B442">
         <v>2022</v>
@@ -14654,19 +14654,19 @@
         <v>1</v>
       </c>
       <c r="E442" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F442" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G442" t="s">
         <v>25</v>
       </c>
       <c r="H442">
-        <v>62</v>
+        <v>83</v>
       </c>
       <c r="I442">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="J442">
         <v>0</v>
@@ -14674,7 +14674,7 @@
     </row>
     <row r="443" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A443" s="1">
-        <v>44793</v>
+        <v>44791</v>
       </c>
       <c r="B443">
         <v>2022</v>
@@ -14686,19 +14686,19 @@
         <v>1</v>
       </c>
       <c r="E443" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F443" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G443" t="s">
         <v>26</v>
       </c>
       <c r="H443">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="I443">
-        <v>62</v>
+        <v>83</v>
       </c>
       <c r="J443">
         <v>0</v>
@@ -14718,19 +14718,19 @@
         <v>1</v>
       </c>
       <c r="E444" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F444" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="G444" t="s">
         <v>25</v>
       </c>
       <c r="H444">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="I444">
-        <v>117</v>
+        <v>100</v>
       </c>
       <c r="J444">
         <v>0</v>
@@ -14750,19 +14750,19 @@
         <v>1</v>
       </c>
       <c r="E445" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F445" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G445" t="s">
         <v>26</v>
       </c>
       <c r="H445">
-        <v>117</v>
+        <v>100</v>
       </c>
       <c r="I445">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="J445">
         <v>0</v>
@@ -14770,7 +14770,7 @@
     </row>
     <row r="446" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A446" s="1">
-        <v>44794</v>
+        <v>44793</v>
       </c>
       <c r="B446">
         <v>2022</v>
@@ -14782,19 +14782,19 @@
         <v>1</v>
       </c>
       <c r="E446" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="F446" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="G446" t="s">
         <v>25</v>
       </c>
       <c r="H446">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="I446">
-        <v>79</v>
+        <v>117</v>
       </c>
       <c r="J446">
         <v>0</v>
@@ -14802,7 +14802,7 @@
     </row>
     <row r="447" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A447" s="1">
-        <v>44794</v>
+        <v>44793</v>
       </c>
       <c r="B447">
         <v>2022</v>
@@ -14814,19 +14814,19 @@
         <v>1</v>
       </c>
       <c r="E447" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F447" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="G447" t="s">
         <v>26</v>
       </c>
       <c r="H447">
-        <v>79</v>
+        <v>117</v>
       </c>
       <c r="I447">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="J447">
         <v>0</v>
@@ -14846,19 +14846,19 @@
         <v>1</v>
       </c>
       <c r="E448" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="F448" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G448" t="s">
         <v>25</v>
       </c>
       <c r="H448">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="I448">
-        <v>97</v>
+        <v>79</v>
       </c>
       <c r="J448">
         <v>0</v>
@@ -14878,19 +14878,19 @@
         <v>1</v>
       </c>
       <c r="E449" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F449" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="G449" t="s">
         <v>26</v>
       </c>
       <c r="H449">
-        <v>97</v>
+        <v>79</v>
       </c>
       <c r="I449">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="J449">
         <v>0</v>
@@ -14898,7 +14898,7 @@
     </row>
     <row r="450" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A450" s="1">
-        <v>44796</v>
+        <v>44794</v>
       </c>
       <c r="B450">
         <v>2022</v>
@@ -14910,19 +14910,19 @@
         <v>1</v>
       </c>
       <c r="E450" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="F450" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="G450" t="s">
         <v>25</v>
       </c>
       <c r="H450">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="I450">
-        <v>72</v>
+        <v>97</v>
       </c>
       <c r="J450">
         <v>0</v>
@@ -14930,7 +14930,7 @@
     </row>
     <row r="451" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A451" s="1">
-        <v>44796</v>
+        <v>44794</v>
       </c>
       <c r="B451">
         <v>2022</v>
@@ -14942,19 +14942,19 @@
         <v>1</v>
       </c>
       <c r="E451" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F451" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="G451" t="s">
         <v>26</v>
       </c>
       <c r="H451">
-        <v>72</v>
+        <v>97</v>
       </c>
       <c r="I451">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="J451">
         <v>0</v>
@@ -14962,7 +14962,7 @@
     </row>
     <row r="452" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A452" s="1">
-        <v>44797</v>
+        <v>44796</v>
       </c>
       <c r="B452">
         <v>2022</v>
@@ -14974,19 +14974,19 @@
         <v>1</v>
       </c>
       <c r="E452" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F452" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="G452" t="s">
         <v>25</v>
       </c>
       <c r="H452">
-        <v>73</v>
+        <v>90</v>
       </c>
       <c r="I452">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="J452">
         <v>0</v>
@@ -14994,7 +14994,7 @@
     </row>
     <row r="453" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A453" s="1">
-        <v>44797</v>
+        <v>44796</v>
       </c>
       <c r="B453">
         <v>2022</v>
@@ -15006,19 +15006,19 @@
         <v>1</v>
       </c>
       <c r="E453" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="F453" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G453" t="s">
         <v>26</v>
       </c>
       <c r="H453">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="I453">
-        <v>73</v>
+        <v>90</v>
       </c>
       <c r="J453">
         <v>0</v>
@@ -15026,7 +15026,7 @@
     </row>
     <row r="454" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A454" s="1">
-        <v>44801</v>
+        <v>44797</v>
       </c>
       <c r="B454">
         <v>2022</v>
@@ -15035,22 +15035,22 @@
         <v>23</v>
       </c>
       <c r="D454">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E454" t="s">
         <v>19</v>
       </c>
       <c r="F454" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G454" t="s">
         <v>25</v>
       </c>
       <c r="H454">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="I454">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="J454">
         <v>0</v>
@@ -15058,7 +15058,7 @@
     </row>
     <row r="455" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A455" s="1">
-        <v>44801</v>
+        <v>44797</v>
       </c>
       <c r="B455">
         <v>2022</v>
@@ -15067,10 +15067,10 @@
         <v>23</v>
       </c>
       <c r="D455">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E455" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F455" t="s">
         <v>19</v>
@@ -15079,10 +15079,10 @@
         <v>26</v>
       </c>
       <c r="H455">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="I455">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="J455">
         <v>0</v>
@@ -15102,19 +15102,19 @@
         <v>2</v>
       </c>
       <c r="E456" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F456" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="G456" t="s">
         <v>25</v>
       </c>
       <c r="H456">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="I456">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="J456">
         <v>0</v>
@@ -15134,19 +15134,19 @@
         <v>2</v>
       </c>
       <c r="E457" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F457" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G457" t="s">
         <v>26</v>
       </c>
       <c r="H457">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="I457">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="J457">
         <v>0</v>
@@ -15154,7 +15154,7 @@
     </row>
     <row r="458" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A458" s="1">
-        <v>44804</v>
+        <v>44801</v>
       </c>
       <c r="B458">
         <v>2022</v>
@@ -15166,19 +15166,19 @@
         <v>2</v>
       </c>
       <c r="E458" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F458" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="G458" t="s">
         <v>25</v>
       </c>
       <c r="H458">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I458">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="J458">
         <v>0</v>
@@ -15186,7 +15186,7 @@
     </row>
     <row r="459" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A459" s="1">
-        <v>44804</v>
+        <v>44801</v>
       </c>
       <c r="B459">
         <v>2022</v>
@@ -15198,19 +15198,19 @@
         <v>2</v>
       </c>
       <c r="E459" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F459" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G459" t="s">
         <v>26</v>
       </c>
       <c r="H459">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="I459">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="J459">
         <v>0</v>
@@ -15230,19 +15230,19 @@
         <v>2</v>
       </c>
       <c r="E460" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F460" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="G460" t="s">
         <v>25</v>
       </c>
       <c r="H460">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="I460">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="J460">
         <v>0</v>
@@ -15262,19 +15262,19 @@
         <v>2</v>
       </c>
       <c r="E461" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F461" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G461" t="s">
         <v>26</v>
       </c>
       <c r="H461">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="I461">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="J461">
         <v>0</v>
@@ -15282,7 +15282,7 @@
     </row>
     <row r="462" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A462" s="1">
-        <v>44808</v>
+        <v>44804</v>
       </c>
       <c r="B462">
         <v>2022</v>
@@ -15294,19 +15294,19 @@
         <v>2</v>
       </c>
       <c r="E462" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F462" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="G462" t="s">
         <v>25</v>
       </c>
       <c r="H462">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="I462">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="J462">
         <v>0</v>
@@ -15314,7 +15314,7 @@
     </row>
     <row r="463" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A463" s="1">
-        <v>44808</v>
+        <v>44804</v>
       </c>
       <c r="B463">
         <v>2022</v>
@@ -15326,19 +15326,19 @@
         <v>2</v>
       </c>
       <c r="E463" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F463" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G463" t="s">
         <v>26</v>
       </c>
       <c r="H463">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="I463">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="J463">
         <v>0</v>
@@ -15358,22 +15358,22 @@
         <v>2</v>
       </c>
       <c r="E464" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F464" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G464" t="s">
         <v>25</v>
       </c>
       <c r="H464">
-        <v>110</v>
+        <v>76</v>
       </c>
       <c r="I464">
-        <v>98</v>
+        <v>72</v>
       </c>
       <c r="J464">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="465" spans="1:10" x14ac:dyDescent="0.35">
@@ -15390,27 +15390,27 @@
         <v>2</v>
       </c>
       <c r="E465" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F465" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="G465" t="s">
         <v>26</v>
       </c>
       <c r="H465">
-        <v>98</v>
+        <v>72</v>
       </c>
       <c r="I465">
-        <v>110</v>
+        <v>76</v>
       </c>
       <c r="J465">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="466" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A466" s="1">
-        <v>44810</v>
+        <v>44808</v>
       </c>
       <c r="B466">
         <v>2022</v>
@@ -15422,27 +15422,27 @@
         <v>2</v>
       </c>
       <c r="E466" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F466" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G466" t="s">
         <v>25</v>
       </c>
       <c r="H466">
-        <v>80</v>
+        <v>110</v>
       </c>
       <c r="I466">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="J466">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="467" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A467" s="1">
-        <v>44810</v>
+        <v>44808</v>
       </c>
       <c r="B467">
         <v>2022</v>
@@ -15454,22 +15454,22 @@
         <v>2</v>
       </c>
       <c r="E467" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F467" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="G467" t="s">
         <v>26</v>
       </c>
       <c r="H467">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="I467">
-        <v>80</v>
+        <v>110</v>
       </c>
       <c r="J467">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="468" spans="1:10" x14ac:dyDescent="0.35">
@@ -15486,19 +15486,19 @@
         <v>2</v>
       </c>
       <c r="E468" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F468" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G468" t="s">
         <v>25</v>
       </c>
       <c r="H468">
-        <v>97</v>
+        <v>80</v>
       </c>
       <c r="I468">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="J468">
         <v>0</v>
@@ -15518,19 +15518,19 @@
         <v>2</v>
       </c>
       <c r="E469" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F469" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="G469" t="s">
         <v>26</v>
       </c>
       <c r="H469">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="I469">
-        <v>97</v>
+        <v>80</v>
       </c>
       <c r="J469">
         <v>0</v>
@@ -15538,7 +15538,7 @@
     </row>
     <row r="470" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A470" s="1">
-        <v>44812</v>
+        <v>44810</v>
       </c>
       <c r="B470">
         <v>2022</v>
@@ -15550,19 +15550,19 @@
         <v>2</v>
       </c>
       <c r="E470" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F470" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G470" t="s">
         <v>25</v>
       </c>
       <c r="H470">
-        <v>72</v>
+        <v>97</v>
       </c>
       <c r="I470">
-        <v>63</v>
+        <v>92</v>
       </c>
       <c r="J470">
         <v>0</v>
@@ -15570,7 +15570,7 @@
     </row>
     <row r="471" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A471" s="1">
-        <v>44812</v>
+        <v>44810</v>
       </c>
       <c r="B471">
         <v>2022</v>
@@ -15582,19 +15582,19 @@
         <v>2</v>
       </c>
       <c r="E471" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F471" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="G471" t="s">
         <v>26</v>
       </c>
       <c r="H471">
-        <v>63</v>
+        <v>92</v>
       </c>
       <c r="I471">
-        <v>72</v>
+        <v>97</v>
       </c>
       <c r="J471">
         <v>0</v>
@@ -15602,7 +15602,7 @@
     </row>
     <row r="472" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A472" s="1">
-        <v>44815</v>
+        <v>44812</v>
       </c>
       <c r="B472">
         <v>2022</v>
@@ -15611,22 +15611,22 @@
         <v>23</v>
       </c>
       <c r="D472">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E472" t="s">
         <v>19</v>
       </c>
       <c r="F472" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="G472" t="s">
         <v>25</v>
       </c>
       <c r="H472">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="I472">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="J472">
         <v>0</v>
@@ -15634,7 +15634,7 @@
     </row>
     <row r="473" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A473" s="1">
-        <v>44815</v>
+        <v>44812</v>
       </c>
       <c r="B473">
         <v>2022</v>
@@ -15643,10 +15643,10 @@
         <v>23</v>
       </c>
       <c r="D473">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E473" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F473" t="s">
         <v>19</v>
@@ -15655,10 +15655,10 @@
         <v>26</v>
       </c>
       <c r="H473">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="I473">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="J473">
         <v>0</v>
@@ -15666,7 +15666,7 @@
     </row>
     <row r="474" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A474" s="1">
-        <v>44817</v>
+        <v>44815</v>
       </c>
       <c r="B474">
         <v>2022</v>
@@ -15687,10 +15687,10 @@
         <v>25</v>
       </c>
       <c r="H474">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="I474">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="J474">
         <v>0</v>
@@ -15698,7 +15698,7 @@
     </row>
     <row r="475" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A475" s="1">
-        <v>44817</v>
+        <v>44815</v>
       </c>
       <c r="B475">
         <v>2022</v>
@@ -15719,10 +15719,10 @@
         <v>26</v>
       </c>
       <c r="H475">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="I475">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="J475">
         <v>0</v>
@@ -15730,7 +15730,7 @@
     </row>
     <row r="476" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A476" s="1">
-        <v>44819</v>
+        <v>44817</v>
       </c>
       <c r="B476">
         <v>2022</v>
@@ -15742,19 +15742,19 @@
         <v>3</v>
       </c>
       <c r="E476" t="s">
+        <v>19</v>
+      </c>
+      <c r="F476" t="s">
         <v>24</v>
       </c>
-      <c r="F476" t="s">
-        <v>19</v>
-      </c>
       <c r="G476" t="s">
         <v>25</v>
       </c>
       <c r="H476">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="I476">
-        <v>105</v>
+        <v>85</v>
       </c>
       <c r="J476">
         <v>0</v>
@@ -15762,7 +15762,7 @@
     </row>
     <row r="477" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A477" s="1">
-        <v>44819</v>
+        <v>44817</v>
       </c>
       <c r="B477">
         <v>2022</v>
@@ -15774,19 +15774,19 @@
         <v>3</v>
       </c>
       <c r="E477" t="s">
+        <v>24</v>
+      </c>
+      <c r="F477" t="s">
         <v>19</v>
       </c>
-      <c r="F477" t="s">
-        <v>24</v>
-      </c>
       <c r="G477" t="s">
         <v>26</v>
       </c>
       <c r="H477">
-        <v>105</v>
+        <v>85</v>
       </c>
       <c r="I477">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="J477">
         <v>0</v>
@@ -15794,7 +15794,7 @@
     </row>
     <row r="478" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A478" s="1">
-        <v>44822</v>
+        <v>44819</v>
       </c>
       <c r="B478">
         <v>2022</v>
@@ -15815,10 +15815,10 @@
         <v>25</v>
       </c>
       <c r="H478">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="I478">
-        <v>71</v>
+        <v>105</v>
       </c>
       <c r="J478">
         <v>0</v>
@@ -15826,7 +15826,7 @@
     </row>
     <row r="479" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A479" s="1">
-        <v>44822</v>
+        <v>44819</v>
       </c>
       <c r="B479">
         <v>2022</v>
@@ -15847,12 +15847,76 @@
         <v>26</v>
       </c>
       <c r="H479">
+        <v>105</v>
+      </c>
+      <c r="I479">
+        <v>76</v>
+      </c>
+      <c r="J479">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="480" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A480" s="1">
+        <v>44822</v>
+      </c>
+      <c r="B480">
+        <v>2022</v>
+      </c>
+      <c r="C480" t="s">
+        <v>23</v>
+      </c>
+      <c r="D480">
+        <v>3</v>
+      </c>
+      <c r="E480" t="s">
+        <v>24</v>
+      </c>
+      <c r="F480" t="s">
+        <v>19</v>
+      </c>
+      <c r="G480" t="s">
+        <v>25</v>
+      </c>
+      <c r="H480">
+        <v>78</v>
+      </c>
+      <c r="I480">
         <v>71</v>
       </c>
-      <c r="I479">
+      <c r="J480">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="481" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A481" s="1">
+        <v>44822</v>
+      </c>
+      <c r="B481">
+        <v>2022</v>
+      </c>
+      <c r="C481" t="s">
+        <v>23</v>
+      </c>
+      <c r="D481">
+        <v>3</v>
+      </c>
+      <c r="E481" t="s">
+        <v>19</v>
+      </c>
+      <c r="F481" t="s">
+        <v>24</v>
+      </c>
+      <c r="G481" t="s">
+        <v>26</v>
+      </c>
+      <c r="H481">
+        <v>71</v>
+      </c>
+      <c r="I481">
         <v>78</v>
       </c>
-      <c r="J479">
+      <c r="J481">
         <v>0</v>
       </c>
     </row>
